--- a/lomonsov 2026/explore_data/_WDI_diff.xlsx
+++ b/lomonsov 2026/explore_data/_WDI_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -402,953 +402,897 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>97480773262.83704</v>
+        <v>181299468453.5659</v>
       </c>
       <c r="B2">
-        <v>107415673550.5941</v>
+        <v>311025036670.6763</v>
       </c>
       <c r="C2">
-        <v>6091854869.855494</v>
+        <v>80319410038.41977</v>
       </c>
       <c r="D2">
-        <v>23002415613.38635</v>
+        <v>43612618970.65457</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>162837200786.6289</v>
+        <v>193853810459.5862</v>
       </c>
       <c r="B3">
-        <v>116804622501.2604</v>
+        <v>2323724252.332764</v>
       </c>
       <c r="C3">
-        <v>50263286501.70332</v>
+        <v>-6246852734.867676</v>
       </c>
       <c r="D3">
-        <v>38557965820.23837</v>
+        <v>62721791270.50177</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>181299468453.5659</v>
+        <v>184991921989.8369</v>
       </c>
       <c r="B4">
-        <v>311025036670.6763</v>
+        <v>126416308570.4297</v>
       </c>
       <c r="C4">
-        <v>80319410038.41977</v>
+        <v>-22880368369.04453</v>
       </c>
       <c r="D4">
-        <v>43612618970.65457</v>
+        <v>23165541363.70654</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>193853810459.5862</v>
+        <v>185730412688.4399</v>
       </c>
       <c r="B5">
-        <v>2323724252.332764</v>
+        <v>261680247948.1042</v>
       </c>
       <c r="C5">
-        <v>-6246852734.867676</v>
+        <v>164516234723.7073</v>
       </c>
       <c r="D5">
-        <v>62721791270.50177</v>
+        <v>32403685878.94525</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>184991921989.8369</v>
+        <v>190161356923.3152</v>
       </c>
       <c r="B6">
-        <v>126416308570.4297</v>
+        <v>329101707098.4167</v>
       </c>
       <c r="C6">
-        <v>-22880368369.04453</v>
+        <v>212656521678.4025</v>
       </c>
       <c r="D6">
-        <v>23165541363.70654</v>
+        <v>68457740346.63232</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>185730412688.4399</v>
+        <v>177237769567.9927</v>
       </c>
       <c r="B7">
-        <v>261680247948.1042</v>
+        <v>369894609634.5583</v>
       </c>
       <c r="C7">
-        <v>164516234723.7073</v>
+        <v>63227096038.42114</v>
       </c>
       <c r="D7">
-        <v>32403685878.94525</v>
+        <v>6074151476.997009</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>190161356923.3152</v>
+        <v>186838148750.7632</v>
       </c>
       <c r="B8">
-        <v>329101707098.4167</v>
+        <v>325752789053.9282</v>
       </c>
       <c r="C8">
-        <v>212656521678.4025</v>
+        <v>246300973015.7943</v>
       </c>
       <c r="D8">
-        <v>68457740346.63232</v>
+        <v>28837777465.53455</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>177237769567.9927</v>
+        <v>223393438720.918</v>
       </c>
       <c r="B9">
-        <v>369894609634.5583</v>
+        <v>261208708258.5732</v>
       </c>
       <c r="C9">
-        <v>63227096038.42114</v>
+        <v>575288329618.571</v>
       </c>
       <c r="D9">
-        <v>6074151476.997009</v>
+        <v>115950613616.139</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>186838148750.7632</v>
+        <v>234840044679.0332</v>
       </c>
       <c r="B10">
-        <v>325752789053.9282</v>
+        <v>220978199872.6465</v>
       </c>
       <c r="C10">
-        <v>246300973015.7943</v>
+        <v>-159353926823.4951</v>
       </c>
       <c r="D10">
-        <v>28837777465.53455</v>
+        <v>30089355627.2738</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>223393438720.918</v>
+        <v>282841940592.8838</v>
       </c>
       <c r="B11">
-        <v>261208708258.5732</v>
+        <v>548494472694.7925</v>
       </c>
       <c r="C11">
-        <v>575288329618.571</v>
+        <v>-145425156197.6567</v>
       </c>
       <c r="D11">
-        <v>115950613616.139</v>
+        <v>132807442300.0691</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>234840044679.0332</v>
+        <v>338228743579.2778</v>
       </c>
       <c r="B12">
-        <v>220978199872.6465</v>
+        <v>684144546546.9644</v>
       </c>
       <c r="C12">
-        <v>-159353926823.4951</v>
+        <v>56612449790.35742</v>
       </c>
       <c r="D12">
-        <v>30089355627.2738</v>
+        <v>232063348941.5715</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>282841940592.8838</v>
+        <v>372937806802.9243</v>
       </c>
       <c r="B13">
-        <v>548494472694.7925</v>
+        <v>178435509351.3135</v>
       </c>
       <c r="C13">
-        <v>-145425156197.6567</v>
+        <v>-206625196990.911</v>
       </c>
       <c r="D13">
-        <v>132807442300.0691</v>
+        <v>261665755572.2413</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>338228743579.2778</v>
+        <v>464510654395.751</v>
       </c>
       <c r="B14">
-        <v>684144546546.9644</v>
+        <v>245174454521.1729</v>
       </c>
       <c r="C14">
-        <v>56612449790.35742</v>
+        <v>-131266220115.3019</v>
       </c>
       <c r="D14">
-        <v>232063348941.5715</v>
+        <v>266853260092.895</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>372937806802.9243</v>
+        <v>572699542909.0088</v>
       </c>
       <c r="B15">
-        <v>178435509351.3135</v>
+        <v>494335487351.752</v>
       </c>
       <c r="C15">
-        <v>-206625196990.911</v>
+        <v>1305610370189.478</v>
       </c>
       <c r="D15">
-        <v>261665755572.2413</v>
+        <v>300972576281.2585</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>464510654395.751</v>
+        <v>720397684215.6689</v>
       </c>
       <c r="B16">
-        <v>245174454521.1729</v>
+        <v>577222237962.9092</v>
       </c>
       <c r="C16">
-        <v>-131266220115.3019</v>
+        <v>5133099134122.242</v>
       </c>
       <c r="D16">
-        <v>266853260092.895</v>
+        <v>219894166002.2209</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>572699542909.0088</v>
+        <v>561991427663.915</v>
       </c>
       <c r="B17">
-        <v>494335487351.752</v>
+        <v>343299616590.8428</v>
       </c>
       <c r="C17">
-        <v>1305610370189.478</v>
+        <v>-4793150663269.371</v>
       </c>
       <c r="D17">
-        <v>300972576281.2585</v>
+        <v>16809506748.12158</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>720397684215.6689</v>
+        <v>599285208347.0908</v>
       </c>
       <c r="B18">
-        <v>577222237962.9092</v>
+        <v>2128304587798.155</v>
       </c>
       <c r="C18">
-        <v>5133099134122.242</v>
+        <v>2371928493423.854</v>
       </c>
       <c r="D18">
-        <v>219894166002.2209</v>
+        <v>-348887314886.9307</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>561991427663.915</v>
+        <v>738859951868.1895</v>
       </c>
       <c r="B19">
-        <v>343299616590.8428</v>
+        <v>1067466011806.467</v>
       </c>
       <c r="C19">
-        <v>-4793150663269.371</v>
+        <v>214961101190.5068</v>
       </c>
       <c r="D19">
-        <v>16809506748.12158</v>
+        <v>364231878522.3413</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>599285208347.0908</v>
+        <v>729628818049.1387</v>
       </c>
       <c r="B20">
-        <v>2128304587798.155</v>
+        <v>632783454105.2656</v>
       </c>
       <c r="C20">
-        <v>2371928493423.854</v>
+        <v>-1261546952606.954</v>
       </c>
       <c r="D20">
-        <v>-348887314886.9307</v>
+        <v>146788551152.8716</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>738859951868.1895</v>
+        <v>663164654453.9326</v>
       </c>
       <c r="B21">
-        <v>1067466011806.467</v>
+        <v>1318181089786.342</v>
       </c>
       <c r="C21">
-        <v>214961101190.5068</v>
+        <v>126643526272.3062</v>
       </c>
       <c r="D21">
-        <v>364231878522.3413</v>
+        <v>75540597624.66846</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>729628818049.1387</v>
+        <v>708212587544.5332</v>
       </c>
       <c r="B22">
-        <v>632783454105.2656</v>
+        <v>1400495729677.941</v>
       </c>
       <c r="C22">
-        <v>-1261546952606.954</v>
+        <v>96319000764.76318</v>
       </c>
       <c r="D22">
-        <v>146788551152.8716</v>
+        <v>87971021573.23145</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>663164654453.9326</v>
+        <v>732213535523.0898</v>
       </c>
       <c r="B23">
-        <v>1318181089786.342</v>
+        <v>1565519937148.391</v>
       </c>
       <c r="C23">
-        <v>126643526272.3062</v>
+        <v>1954685168756.523</v>
       </c>
       <c r="D23">
-        <v>75540597624.66846</v>
+        <v>61843677644.15918</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>708212587544.5332</v>
+        <v>735905989044.9297</v>
       </c>
       <c r="B24">
-        <v>1400495729677.941</v>
+        <v>2367054986719.711</v>
       </c>
       <c r="C24">
-        <v>96319000764.76318</v>
+        <v>2255991706112.693</v>
       </c>
       <c r="D24">
-        <v>87971021573.23145</v>
+        <v>-70821847177.91797</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>732213535523.0898</v>
+        <v>764337881258.3691</v>
       </c>
       <c r="B25">
-        <v>1565519937148.391</v>
+        <v>1572950628600.016</v>
       </c>
       <c r="C25">
-        <v>1954685168756.523</v>
+        <v>-490810342574.5176</v>
       </c>
       <c r="D25">
-        <v>61843677644.15918</v>
+        <v>-48988004089.04492</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>735905989044.9297</v>
+        <v>830063554126.1309</v>
       </c>
       <c r="B26">
-        <v>2367054986719.711</v>
+        <v>1129581798526.582</v>
       </c>
       <c r="C26">
-        <v>2255991706112.693</v>
+        <v>1248667047993.812</v>
       </c>
       <c r="D26">
-        <v>-70821847177.91797</v>
+        <v>176395142708.9551</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>764337881258.3691</v>
+        <v>869942052283.2598</v>
       </c>
       <c r="B27">
-        <v>1572950628600.016</v>
+        <v>1721951427931.305</v>
       </c>
       <c r="C27">
-        <v>-490810342574.5176</v>
+        <v>-2800985392684.674</v>
       </c>
       <c r="D27">
-        <v>-48988004089.04492</v>
+        <v>90533464085.19189</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>830063554126.1309</v>
+        <v>834125253011.7109</v>
       </c>
       <c r="B28">
-        <v>1129581798526.582</v>
+        <v>2344865719185.309</v>
       </c>
       <c r="C28">
-        <v>1248667047993.812</v>
+        <v>2435872655466.213</v>
       </c>
       <c r="D28">
-        <v>176395142708.9551</v>
+        <v>52355054693.80615</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>869942052283.2598</v>
+        <v>341182706416.9395</v>
       </c>
       <c r="B29">
-        <v>1721951427931.305</v>
+        <v>3074465813156.426</v>
       </c>
       <c r="C29">
-        <v>-2800985392684.674</v>
+        <v>3633828451186.242</v>
       </c>
       <c r="D29">
-        <v>90533464085.19189</v>
+        <v>83666620256.23535</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>834125253011.7109</v>
+        <v>1278696658343.32</v>
       </c>
       <c r="B30">
-        <v>2344865719185.309</v>
+        <v>1391212397196.16</v>
       </c>
       <c r="C30">
-        <v>2435872655466.213</v>
+        <v>634458535797.8711</v>
       </c>
       <c r="D30">
-        <v>52355054693.80615</v>
+        <v>447028453882.3999</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>341182706416.9395</v>
+        <v>507712360739.8398</v>
       </c>
       <c r="B31">
-        <v>3074465813156.426</v>
+        <v>2256241121239.363</v>
       </c>
       <c r="C31">
-        <v>3633828451186.242</v>
+        <v>-2387763353632.803</v>
       </c>
       <c r="D31">
-        <v>83666620256.23535</v>
+        <v>228028928190.417</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>1278696658343.32</v>
+        <v>904651115478.0703</v>
       </c>
       <c r="B32">
-        <v>1391212397196.16</v>
+        <v>3022015234510.25</v>
       </c>
       <c r="C32">
-        <v>634458535797.8711</v>
+        <v>80211343573.10156</v>
       </c>
       <c r="D32">
-        <v>447028453882.3999</v>
+        <v>-26879869566.48828</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>507712360739.8398</v>
+        <v>876588468642.7773</v>
       </c>
       <c r="B33">
-        <v>2256241121239.363</v>
+        <v>2504996921283.121</v>
       </c>
       <c r="C33">
-        <v>-2387763353632.803</v>
+        <v>1053896810453.139</v>
       </c>
       <c r="D33">
-        <v>228028928190.417</v>
+        <v>337622978136.2988</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>904651115478.0703</v>
+        <v>23560794793.0733</v>
       </c>
       <c r="B34">
-        <v>3022015234510.25</v>
+        <v>1319301786.737274</v>
       </c>
       <c r="C34">
-        <v>80211343573.10156</v>
+        <v>69050133663.27808</v>
       </c>
       <c r="D34">
-        <v>-26879869566.48828</v>
+        <v>7233183318.350037</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>876588468642.7773</v>
+        <v>34592876438.10217</v>
       </c>
       <c r="B35">
-        <v>2504996921283.121</v>
+        <v>7220712950.116211</v>
       </c>
       <c r="C35">
-        <v>1053896810453.139</v>
+        <v>33833362713.31134</v>
       </c>
       <c r="D35">
-        <v>337622978136.2988</v>
+        <v>3700412566.347641</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>4916832599.445557</v>
+        <v>41969453404.57202</v>
       </c>
       <c r="B36">
-        <v>-3921794464.162064</v>
+        <v>3150053924.517593</v>
       </c>
       <c r="C36">
-        <v>26613627463.46481</v>
+        <v>-6159649353.756989</v>
       </c>
       <c r="D36">
-        <v>7121287675.830563</v>
+        <v>9847600773.139946</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>25776015270.51233</v>
+        <v>44999592792.89319</v>
       </c>
       <c r="B37">
-        <v>10487151967.51886</v>
+        <v>15845865360.39709</v>
       </c>
       <c r="C37">
-        <v>28492438792.87169</v>
+        <v>-10217240499.3277</v>
       </c>
       <c r="D37">
-        <v>3918735882.629959</v>
+        <v>1938573414.265701</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>23560794793.0733</v>
+        <v>25961717025.10535</v>
       </c>
       <c r="B38">
-        <v>1319301786.737274</v>
+        <v>7095438218.256195</v>
       </c>
       <c r="C38">
-        <v>69050133663.27808</v>
+        <v>5901477079.465515</v>
       </c>
       <c r="D38">
-        <v>7233183318.350037</v>
+        <v>4734235219.25042</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>34592876438.10217</v>
+        <v>41251298081.00183</v>
       </c>
       <c r="B39">
-        <v>7220712950.116211</v>
+        <v>10583954053.97128</v>
       </c>
       <c r="C39">
-        <v>33833362713.31134</v>
+        <v>-28730207950.69763</v>
       </c>
       <c r="D39">
-        <v>3700412566.347641</v>
+        <v>6731432434.225296</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>41969453404.57202</v>
+        <v>62651958691.88062</v>
       </c>
       <c r="B40">
-        <v>3150053924.517593</v>
+        <v>28288074430.61987</v>
       </c>
       <c r="C40">
-        <v>-6159649353.756989</v>
+        <v>131063497488.7971</v>
       </c>
       <c r="D40">
-        <v>9847600773.139946</v>
+        <v>10245975333.32219</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>44999592792.89319</v>
+        <v>29611098878.51379</v>
       </c>
       <c r="B41">
-        <v>15845865360.39709</v>
+        <v>30877089575.45758</v>
       </c>
       <c r="C41">
-        <v>-10217240499.3277</v>
+        <v>80823560476.42615</v>
       </c>
       <c r="D41">
-        <v>1938573414.265701</v>
+        <v>15760714392.38165</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>25961717025.10535</v>
+        <v>38617513241.20105</v>
       </c>
       <c r="B42">
-        <v>7095438218.256195</v>
+        <v>13292516502.08298</v>
       </c>
       <c r="C42">
-        <v>5901477079.465515</v>
+        <v>-128482655127.6252</v>
       </c>
       <c r="D42">
-        <v>4734235219.25042</v>
+        <v>1336534898.991486</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>41251298081.00183</v>
+        <v>31921134715.27881</v>
       </c>
       <c r="B43">
-        <v>10583954053.97128</v>
+        <v>41252749895.73611</v>
       </c>
       <c r="C43">
-        <v>-28730207950.69763</v>
+        <v>34097131410.33362</v>
       </c>
       <c r="D43">
-        <v>6731432434.225296</v>
+        <v>18869322210.06911</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>62651958691.88062</v>
+        <v>68469670761.91187</v>
       </c>
       <c r="B44">
-        <v>28288074430.61987</v>
+        <v>15729156220.20496</v>
       </c>
       <c r="C44">
-        <v>131063497488.7971</v>
+        <v>186455331826.3823</v>
       </c>
       <c r="D44">
-        <v>10245975333.32219</v>
+        <v>16188832977.27434</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>29611098878.51379</v>
+        <v>74439380355.24182</v>
       </c>
       <c r="B45">
-        <v>30877089575.45758</v>
+        <v>69836140230.14368</v>
       </c>
       <c r="C45">
-        <v>80823560476.42615</v>
+        <v>116440830260.5332</v>
       </c>
       <c r="D45">
-        <v>15760714392.38165</v>
+        <v>40646296239.74188</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>38617513241.20105</v>
+        <v>80342174443.27893</v>
       </c>
       <c r="B46">
-        <v>13292516502.08298</v>
+        <v>71495226948.29779</v>
       </c>
       <c r="C46">
-        <v>-128482655127.6252</v>
+        <v>239185011543.9619</v>
       </c>
       <c r="D46">
-        <v>1336534898.991486</v>
+        <v>33456644678.26398</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>31921134715.27881</v>
+        <v>88210559573.2771</v>
       </c>
       <c r="B47">
-        <v>41252749895.73611</v>
+        <v>77439735974.64563</v>
       </c>
       <c r="C47">
-        <v>34097131410.33362</v>
+        <v>292601279342.0759</v>
       </c>
       <c r="D47">
-        <v>18869322210.06911</v>
+        <v>36955843458.15387</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>68469670761.91187</v>
+        <v>90591812765.84106</v>
       </c>
       <c r="B48">
-        <v>15729156220.20496</v>
+        <v>64985863059.04364</v>
       </c>
       <c r="C48">
-        <v>186455331826.3823</v>
+        <v>926830163317.292</v>
       </c>
       <c r="D48">
-        <v>16188832977.27434</v>
+        <v>13305703789.81458</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>74439380355.24182</v>
+        <v>39297577926.78882</v>
       </c>
       <c r="B49">
-        <v>69836140230.14368</v>
+        <v>69529905799.35974</v>
       </c>
       <c r="C49">
-        <v>116440830260.5332</v>
+        <v>-1186541795739.119</v>
       </c>
       <c r="D49">
-        <v>40646296239.74188</v>
+        <v>51453036837.93076</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>80342174443.27893</v>
+        <v>103181339749.26</v>
       </c>
       <c r="B50">
-        <v>71495226948.29779</v>
+        <v>30823227352.51245</v>
       </c>
       <c r="C50">
-        <v>239185011543.9619</v>
+        <v>576183307637.6924</v>
       </c>
       <c r="D50">
-        <v>33456644678.26398</v>
+        <v>-27468669664.28082</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>88210559573.2771</v>
+        <v>120292288576.4531</v>
       </c>
       <c r="B51">
-        <v>77439735974.64563</v>
+        <v>95226558306.02258</v>
       </c>
       <c r="C51">
-        <v>292601279342.0759</v>
+        <v>173078690445.5701</v>
       </c>
       <c r="D51">
-        <v>36955843458.15387</v>
+        <v>55264566960.47394</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>90591812765.84106</v>
+        <v>80501267101.77295</v>
       </c>
       <c r="B52">
-        <v>64985863059.04364</v>
+        <v>52559794767.95715</v>
       </c>
       <c r="C52">
-        <v>926830163317.292</v>
+        <v>-511986009474.5242</v>
       </c>
       <c r="D52">
-        <v>13305703789.81458</v>
+        <v>52615541503.16541</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>39297577926.78882</v>
+        <v>88197004670.3999</v>
       </c>
       <c r="B53">
-        <v>69529905799.35974</v>
+        <v>55450777969.20068</v>
       </c>
       <c r="C53">
-        <v>-1186541795739.119</v>
+        <v>193293029772.0073</v>
       </c>
       <c r="D53">
-        <v>51453036837.93076</v>
+        <v>21541961645.83191</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>103181339749.26</v>
+        <v>108857327262.3101</v>
       </c>
       <c r="B54">
-        <v>30823227352.51245</v>
+        <v>65500967440.96362</v>
       </c>
       <c r="C54">
-        <v>576183307637.6924</v>
+        <v>-61226540422.85645</v>
       </c>
       <c r="D54">
-        <v>-27468669664.28082</v>
+        <v>42963878552.69617</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>120292288576.4531</v>
+        <v>134381034142.322</v>
       </c>
       <c r="B55">
-        <v>95226558306.02258</v>
+        <v>60588679556.02087</v>
       </c>
       <c r="C55">
-        <v>173078690445.5701</v>
+        <v>375611104989.4729</v>
       </c>
       <c r="D55">
-        <v>55264566960.47394</v>
+        <v>-13798929831.01746</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>80501267101.77295</v>
+        <v>155753795135.991</v>
       </c>
       <c r="B56">
-        <v>52559794767.95715</v>
+        <v>80500020722.89038</v>
       </c>
       <c r="C56">
-        <v>-511986009474.5242</v>
+        <v>133974872835.8665</v>
       </c>
       <c r="D56">
-        <v>52615541503.16541</v>
+        <v>-30589981479.79639</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>88197004670.3999</v>
+        <v>173678681505.4229</v>
       </c>
       <c r="B57">
-        <v>55450777969.20068</v>
+        <v>27086824335.94739</v>
       </c>
       <c r="C57">
-        <v>193293029772.0073</v>
+        <v>-12211720822.03369</v>
       </c>
       <c r="D57">
-        <v>21541961645.83191</v>
+        <v>19496228513.95447</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>108857327262.3101</v>
+        <v>154749026947.3892</v>
       </c>
       <c r="B58">
-        <v>65500967440.96362</v>
+        <v>68512417424.09253</v>
       </c>
       <c r="C58">
-        <v>-61226540422.85645</v>
+        <v>611476263574.2651</v>
       </c>
       <c r="D58">
-        <v>42963878552.69617</v>
+        <v>20734571084.27692</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>134381034142.322</v>
+        <v>156958701746.8159</v>
       </c>
       <c r="B59">
-        <v>60588679556.02087</v>
+        <v>116563892414.8906</v>
       </c>
       <c r="C59">
-        <v>375611104989.4729</v>
+        <v>-158344932257.425</v>
       </c>
       <c r="D59">
-        <v>-13798929831.01746</v>
+        <v>58907714235.92407</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>155753795135.991</v>
+        <v>100230525640.7441</v>
       </c>
       <c r="B60">
-        <v>80500020722.89038</v>
+        <v>61326635085.45483</v>
       </c>
       <c r="C60">
-        <v>133974872835.8665</v>
+        <v>-17237166434.83936</v>
       </c>
       <c r="D60">
-        <v>-30589981479.79639</v>
+        <v>-14006054626.86853</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>173678681505.4229</v>
+        <v>-155374878798.769</v>
       </c>
       <c r="B61">
-        <v>27086824335.94739</v>
+        <v>16502654783.45874</v>
       </c>
       <c r="C61">
-        <v>-12211720822.03369</v>
+        <v>249043367839.3792</v>
       </c>
       <c r="D61">
-        <v>19496228513.95447</v>
+        <v>-28538116945.80365</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>154749026947.3892</v>
+        <v>245517841852.2251</v>
       </c>
       <c r="B62">
-        <v>68512417424.09253</v>
+        <v>12553576074.59448</v>
       </c>
       <c r="C62">
-        <v>611476263574.2651</v>
+        <v>695567654106.5186</v>
       </c>
       <c r="D62">
-        <v>20734571084.27692</v>
+        <v>121374851378.437</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>156958701746.8159</v>
+        <v>211490753023.6938</v>
       </c>
       <c r="B63">
-        <v>116563892414.8906</v>
+        <v>268563500998.748</v>
       </c>
       <c r="C63">
-        <v>-158344932257.425</v>
+        <v>-85744966609.76611</v>
       </c>
       <c r="D63">
-        <v>58907714235.92407</v>
+        <v>100659030739.8708</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>100230525640.7441</v>
+        <v>274880683948.7812</v>
       </c>
       <c r="B64">
-        <v>61326635085.45483</v>
+        <v>289920878929.9534</v>
       </c>
       <c r="C64">
-        <v>-17237166434.83936</v>
+        <v>867759258404.98</v>
       </c>
       <c r="D64">
-        <v>-14006054626.86853</v>
+        <v>5038182799.870972</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>-155374878798.769</v>
+        <v>212100836915.2368</v>
       </c>
       <c r="B65">
-        <v>16502654783.45874</v>
+        <v>155619851170.7561</v>
       </c>
       <c r="C65">
-        <v>249043367839.3792</v>
+        <v>668864288797.8477</v>
       </c>
       <c r="D65">
-        <v>-28538116945.80365</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66">
-        <v>245517841852.2251</v>
-      </c>
-      <c r="B66">
-        <v>12553576074.59448</v>
-      </c>
-      <c r="C66">
-        <v>695567654106.5186</v>
-      </c>
-      <c r="D66">
-        <v>121374851378.437</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67">
-        <v>211490753023.6938</v>
-      </c>
-      <c r="B67">
-        <v>268563500998.748</v>
-      </c>
-      <c r="C67">
-        <v>-85744966609.76611</v>
-      </c>
-      <c r="D67">
-        <v>100659030739.8708</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68">
-        <v>274880683948.7812</v>
-      </c>
-      <c r="B68">
-        <v>289920878929.9534</v>
-      </c>
-      <c r="C68">
-        <v>867759258404.98</v>
-      </c>
-      <c r="D68">
-        <v>5038182799.870972</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69">
-        <v>212100836915.2368</v>
-      </c>
-      <c r="B69">
-        <v>155619851170.7561</v>
-      </c>
-      <c r="C69">
-        <v>668864288797.8477</v>
-      </c>
-      <c r="D69">
         <v>35516679097.11279</v>
       </c>
     </row>
